--- a/housekeeping/RA Timesheet Sept. and Oct.-1.xlsx
+++ b/housekeeping/RA Timesheet Sept. and Oct.-1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangchen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangchen/Desktop/VAULTs/Working Repo/Tools &amp; Guidelines/USSC_Spider/housekeeping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5AD37E-DDF6-BC45-9FA3-0A102863D172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64276489-ABF2-D44D-8F48-8354278036DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="28800" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Staff No.:</t>
   </si>
@@ -200,6 +200,18 @@
   </si>
   <si>
     <t>Simliarity calculation function - debug and test</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>change similarity function</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>change similarity calculation method, test run, update readme.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix file name length</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -483,48 +495,48 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,12 +950,12 @@
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="10"/>
@@ -970,12 +982,12 @@
       <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -1034,16 +1046,16 @@
       <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="34" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="11"/>
@@ -1072,12 +1084,12 @@
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="10"/>
@@ -1104,12 +1116,12 @@
       <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="33">
         <v>136</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="10"/>
@@ -1136,12 +1148,12 @@
       <c r="A10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="34">
         <v>50</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="10"/>
@@ -1224,13 +1236,13 @@
       <c r="A13" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
       <c r="G13" s="20" t="s">
         <v>23</v>
       </c>
@@ -1260,14 +1272,14 @@
       <c r="A14" s="26">
         <v>45918.19</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="43">
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="29">
         <v>4.5</v>
       </c>
       <c r="H14" s="23">
@@ -1297,13 +1309,13 @@
       <c r="A15" s="26">
         <v>45920.19</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
       <c r="G15" s="22">
         <v>8.5</v>
       </c>
@@ -1334,18 +1346,18 @@
       <c r="A16" s="26">
         <v>45927.19</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
       <c r="G16" s="22">
         <v>2.5</v>
       </c>
       <c r="H16" s="23">
-        <f t="shared" ref="H16:H18" si="0">G16*$B$9</f>
+        <f t="shared" ref="H16:H21" si="0">G16*$B$9</f>
         <v>340</v>
       </c>
       <c r="I16" s="9"/>
@@ -1371,13 +1383,13 @@
       <c r="A17" s="26">
         <v>45949</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
       <c r="G17" s="22">
         <v>4</v>
       </c>
@@ -1408,13 +1420,13 @@
       <c r="A18" s="26">
         <v>45950</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
       <c r="G18" s="22">
         <v>4</v>
       </c>
@@ -1442,14 +1454,23 @@
       <c r="Z18" s="9"/>
     </row>
     <row r="19" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="27"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="23"/>
+      <c r="A19" s="27">
+        <v>45981</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="23">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
@@ -1470,14 +1491,23 @@
       <c r="Z19" s="9"/>
     </row>
     <row r="20" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="27"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="23"/>
+      <c r="A20" s="27">
+        <v>45991</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="28">
+        <v>2</v>
+      </c>
+      <c r="H20" s="23">
+        <f t="shared" si="0"/>
+        <v>272</v>
+      </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
@@ -1497,15 +1527,24 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="26"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="23"/>
+    <row r="21" spans="1:26" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="26">
+        <v>46039</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="22">
+        <v>5</v>
+      </c>
+      <c r="H21" s="23">
+        <f t="shared" si="0"/>
+        <v>680</v>
+      </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -1527,11 +1566,11 @@
     </row>
     <row r="22" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="26"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
       <c r="G22" s="22"/>
       <c r="H22" s="23"/>
       <c r="I22" s="9"/>
@@ -1555,11 +1594,11 @@
     </row>
     <row r="23" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="26"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
       <c r="G23" s="22"/>
       <c r="H23" s="23"/>
       <c r="I23" s="9"/>
@@ -1583,11 +1622,11 @@
     </row>
     <row r="24" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="26"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
       <c r="G24" s="22"/>
       <c r="H24" s="23"/>
       <c r="I24" s="9"/>
@@ -1611,11 +1650,11 @@
     </row>
     <row r="25" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="26"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
       <c r="G25" s="22"/>
       <c r="H25" s="23"/>
       <c r="I25" s="9"/>
@@ -1639,11 +1678,11 @@
     </row>
     <row r="26" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="21"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
       <c r="G26" s="22"/>
       <c r="H26" s="23"/>
       <c r="I26" s="9"/>
@@ -1667,11 +1706,11 @@
     </row>
     <row r="27" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="21"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
       <c r="G27" s="22"/>
       <c r="H27" s="23"/>
       <c r="I27" s="9"/>
@@ -1695,11 +1734,11 @@
     </row>
     <row r="28" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="21"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
       <c r="G28" s="22"/>
       <c r="H28" s="23"/>
       <c r="I28" s="9"/>
@@ -1723,11 +1762,11 @@
     </row>
     <row r="29" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="21"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
       <c r="G29" s="22"/>
       <c r="H29" s="23"/>
       <c r="I29" s="9"/>
@@ -1751,11 +1790,11 @@
     </row>
     <row r="30" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="21"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
       <c r="G30" s="22"/>
       <c r="H30" s="23"/>
       <c r="I30" s="9"/>
@@ -1779,11 +1818,11 @@
     </row>
     <row r="31" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="21"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32"/>
       <c r="G31" s="22"/>
       <c r="H31" s="23"/>
       <c r="I31" s="9"/>
@@ -1807,11 +1846,11 @@
     </row>
     <row r="32" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="21"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
       <c r="G32" s="22"/>
       <c r="H32" s="23"/>
       <c r="I32" s="9"/>
@@ -1835,11 +1874,11 @@
     </row>
     <row r="33" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="21"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32"/>
       <c r="G33" s="22"/>
       <c r="H33" s="23"/>
       <c r="I33" s="9"/>
@@ -1863,11 +1902,11 @@
     </row>
     <row r="34" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="21"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="31"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="32"/>
       <c r="G34" s="22"/>
       <c r="H34" s="23"/>
       <c r="I34" s="9"/>
@@ -1891,11 +1930,11 @@
     </row>
     <row r="35" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="21"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="31"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="32"/>
       <c r="G35" s="22"/>
       <c r="H35" s="23"/>
       <c r="I35" s="9"/>
@@ -1919,11 +1958,11 @@
     </row>
     <row r="36" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="21"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="32"/>
       <c r="G36" s="22"/>
       <c r="H36" s="23"/>
       <c r="I36" s="9"/>
@@ -1947,11 +1986,11 @@
     </row>
     <row r="37" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="21"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="31"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="32"/>
       <c r="G37" s="22"/>
       <c r="H37" s="23"/>
       <c r="I37" s="9"/>
@@ -1974,21 +2013,21 @@
       <c r="Z37" s="9"/>
     </row>
     <row r="38" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="43"/>
       <c r="G38" s="24">
         <f>SUM(G14:G37)</f>
-        <v>23.5</v>
+        <v>31</v>
       </c>
       <c r="H38" s="24">
         <f>SUM(H14:H37)</f>
-        <v>3196</v>
+        <v>4216</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -2155,6 +2194,28 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B7:E7"/>
@@ -2165,28 +2226,6 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2261,27 +2300,27 @@
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="11" spans="1:7" ht="54.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>4</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
@@ -2289,10 +2328,10 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="40">
+      <c r="A14" s="45">
         <v>42401</v>
       </c>
-      <c r="B14" s="40"/>
+      <c r="B14" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/housekeeping/RA Timesheet Sept. and Oct.-1.xlsx
+++ b/housekeeping/RA Timesheet Sept. and Oct.-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangchen/Desktop/VAULTs/Working Repo/Tools &amp; Guidelines/USSC_Spider/housekeeping/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding Projects\USSC_Spider\housekeeping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64276489-ABF2-D44D-8F48-8354278036DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE688E7C-088B-4109-8DF7-BAC691131155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="28800" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3710" yWindow="1280" windowWidth="32660" windowHeight="17930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worklog" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Staff No.:</t>
   </si>
@@ -214,6 +214,10 @@
     <t>fix file name length</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">Re-construct the scraping logic. Implement new scraper for oyez. Integration of two methods. Re-scraping and data cleaning. </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -222,7 +226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -498,40 +502,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -847,20 +851,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.59765625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="19.3984375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="17.796875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="23.6328125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="3.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="3" style="6" customWidth="1"/>
-    <col min="7" max="7" width="35.59765625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="17.3984375" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="6"/>
+    <col min="7" max="7" width="35.6328125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
@@ -890,7 +894,7 @@
       <c r="Y1" s="9"/>
       <c r="Z1" s="9"/>
     </row>
-    <row r="2" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A2" s="5"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -918,7 +922,7 @@
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
     </row>
-    <row r="3" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -946,16 +950,16 @@
       <c r="Y3" s="9"/>
       <c r="Z3" s="9"/>
     </row>
-    <row r="4" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="10"/>
@@ -978,16 +982,16 @@
       <c r="Y4" s="9"/>
       <c r="Z4" s="9"/>
     </row>
-    <row r="5" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="11"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
@@ -1010,7 +1014,7 @@
       <c r="Y5" s="9"/>
       <c r="Z5" s="9"/>
     </row>
-    <row r="6" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -1042,20 +1046,20 @@
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="38" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="11"/>
@@ -1080,16 +1084,16 @@
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="10"/>
@@ -1112,16 +1116,16 @@
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="37">
         <v>136</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="10"/>
@@ -1144,16 +1148,16 @@
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="1:26" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:26" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="38">
         <v>50</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="10"/>
@@ -1176,7 +1180,7 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="1:26" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:26" customFormat="1">
       <c r="A11" s="14"/>
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
@@ -1204,7 +1208,7 @@
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="1:26" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:26" customFormat="1">
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="9"/>
@@ -1232,11 +1236,11 @@
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="1:26" customFormat="1" ht="32" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:26" customFormat="1" ht="30">
       <c r="A13" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="41" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="31"/>
@@ -1268,11 +1272,11 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:26" customFormat="1" ht="37" customHeight="1">
       <c r="A14" s="26">
         <v>45918.19</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="36" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="31"/>
@@ -1305,11 +1309,11 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:26" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="26">
         <v>45920.19</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="36" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="31"/>
@@ -1342,11 +1346,11 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A16" s="26">
         <v>45927.19</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="36" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="31"/>
@@ -1357,7 +1361,7 @@
         <v>2.5</v>
       </c>
       <c r="H16" s="23">
-        <f t="shared" ref="H16:H21" si="0">G16*$B$9</f>
+        <f t="shared" ref="H16:H22" si="0">G16*$B$9</f>
         <v>340</v>
       </c>
       <c r="I16" s="9"/>
@@ -1379,11 +1383,11 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A17" s="26">
         <v>45949</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="36" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="31"/>
@@ -1416,11 +1420,11 @@
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="1:26" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:26" customFormat="1" ht="31" customHeight="1">
       <c r="A18" s="26">
         <v>45950</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="36" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="31"/>
@@ -1453,17 +1457,17 @@
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
     </row>
-    <row r="19" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A19" s="27">
         <v>45981</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="36"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="43"/>
       <c r="G19" s="28">
         <v>0.5</v>
       </c>
@@ -1490,11 +1494,11 @@
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
     </row>
-    <row r="20" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A20" s="27">
         <v>45991</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="36" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="31"/>
@@ -1527,11 +1531,11 @@
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="1:26" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:26" customFormat="1" ht="32" customHeight="1">
       <c r="A21" s="26">
         <v>46039</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="36" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="31"/>
@@ -1564,15 +1568,24 @@
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="26"/>
-      <c r="B22" s="30"/>
+    <row r="22" spans="1:26" customFormat="1" ht="49" customHeight="1">
+      <c r="A22" s="26">
+        <v>46107</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>41</v>
+      </c>
       <c r="C22" s="31"/>
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
       <c r="F22" s="32"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23"/>
+      <c r="G22" s="22">
+        <v>8</v>
+      </c>
+      <c r="H22" s="23">
+        <f t="shared" si="0"/>
+        <v>1088</v>
+      </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
@@ -1592,9 +1605,9 @@
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A23" s="26"/>
-      <c r="B23" s="30"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="31"/>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
@@ -1620,9 +1633,9 @@
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A24" s="26"/>
-      <c r="B24" s="30"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
@@ -1648,9 +1661,9 @@
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
     </row>
-    <row r="25" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A25" s="26"/>
-      <c r="B25" s="30"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
@@ -1676,9 +1689,9 @@
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
     </row>
-    <row r="26" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
@@ -1704,9 +1717,9 @@
       <c r="Y26" s="9"/>
       <c r="Z26" s="9"/>
     </row>
-    <row r="27" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="31"/>
@@ -1732,9 +1745,9 @@
       <c r="Y27" s="9"/>
       <c r="Z27" s="9"/>
     </row>
-    <row r="28" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="40"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="31"/>
       <c r="D28" s="31"/>
       <c r="E28" s="31"/>
@@ -1760,9 +1773,9 @@
       <c r="Y28" s="9"/>
       <c r="Z28" s="9"/>
     </row>
-    <row r="29" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="40"/>
+      <c r="B29" s="30"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
@@ -1788,9 +1801,9 @@
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="30"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="E30" s="31"/>
@@ -1816,9 +1829,9 @@
       <c r="Y30" s="9"/>
       <c r="Z30" s="9"/>
     </row>
-    <row r="31" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="40"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
@@ -1844,9 +1857,9 @@
       <c r="Y31" s="9"/>
       <c r="Z31" s="9"/>
     </row>
-    <row r="32" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="40"/>
+      <c r="B32" s="30"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="E32" s="31"/>
@@ -1872,9 +1885,9 @@
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
     </row>
-    <row r="33" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="40"/>
+      <c r="B33" s="30"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
@@ -1900,9 +1913,9 @@
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A34" s="21"/>
-      <c r="B34" s="40"/>
+      <c r="B34" s="30"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
@@ -1928,9 +1941,9 @@
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
     </row>
-    <row r="35" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A35" s="21"/>
-      <c r="B35" s="40"/>
+      <c r="B35" s="30"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="E35" s="31"/>
@@ -1956,9 +1969,9 @@
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
     </row>
-    <row r="36" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A36" s="21"/>
-      <c r="B36" s="40"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="E36" s="31"/>
@@ -1984,9 +1997,9 @@
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
     </row>
-    <row r="37" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:26" customFormat="1" ht="24" customHeight="1">
       <c r="A37" s="21"/>
-      <c r="B37" s="40"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="31"/>
       <c r="D37" s="31"/>
       <c r="E37" s="31"/>
@@ -2012,22 +2025,22 @@
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
     </row>
-    <row r="38" spans="1:26" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="41" t="s">
+    <row r="38" spans="1:26" customFormat="1" ht="24" customHeight="1">
+      <c r="A38" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="43"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
       <c r="G38" s="24">
         <f>SUM(G14:G37)</f>
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H38" s="24">
         <f>SUM(H14:H37)</f>
-        <v>4216</v>
+        <v>5304</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -2048,7 +2061,7 @@
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
     </row>
-    <row r="39" spans="1:26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2076,7 +2089,7 @@
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
     </row>
-    <row r="40" spans="1:26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -2106,7 +2119,7 @@
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
     </row>
-    <row r="41" spans="1:26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2134,7 +2147,7 @@
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" spans="1:26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -2162,7 +2175,7 @@
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" spans="1:26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:26" customFormat="1" ht="15.75" customHeight="1">
       <c r="A43" s="25" t="s">
         <v>26</v>
       </c>
@@ -2194,28 +2207,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B7:E7"/>
@@ -2226,6 +2217,28 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2243,22 +2256,22 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="3.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="3.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2266,7 +2279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7">
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
@@ -2274,7 +2287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7">
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2285,7 +2298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="30.75" customHeight="1">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
@@ -2296,7 +2309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="30.5" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -2309,7 +2322,7 @@
       <c r="F9" s="44"/>
       <c r="G9" s="44"/>
     </row>
-    <row r="11" spans="1:7" ht="54.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="54.5" customHeight="1">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -2322,12 +2335,12 @@
       <c r="F11" s="44"/>
       <c r="G11" s="44"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7">
       <c r="A14" s="45">
         <v>42401</v>
       </c>
